--- a/output/pdf_financials_xlsx/BGX.xlsx
+++ b/output/pdf_financials_xlsx/BGX.xlsx
@@ -474,10 +474,8 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
@@ -494,20 +492,14 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="6">
@@ -516,10 +508,8 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
@@ -536,20 +526,14 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.162716</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.264019</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.227604</v>
       </c>
     </row>
     <row r="8">
@@ -558,20 +542,14 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -580,20 +558,14 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -618,20 +590,16 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.319908</v>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D11" s="3" t="n">
+        <v>-0.538326</v>
       </c>
     </row>
     <row r="12">
@@ -640,20 +608,14 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -662,20 +624,14 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -684,20 +640,14 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -706,20 +656,14 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>-0.314329</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-0.925499</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-0.538762</v>
       </c>
     </row>
     <row r="16">
@@ -728,20 +672,14 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.285734</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.902845</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-0.536592</v>
       </c>
     </row>
     <row r="17">
@@ -750,20 +688,14 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -816,20 +748,14 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.285734</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.902845</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-0.536592</v>
       </c>
     </row>
     <row r="21">
@@ -838,20 +764,14 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -860,20 +780,14 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -886,12 +800,10 @@
         <v>-0.285734</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-0.285734</v>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.902845</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-0.536592</v>
       </c>
     </row>
     <row r="24">
@@ -966,20 +878,14 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.285734</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.902845</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-0.536592</v>
       </c>
     </row>
     <row r="28">
@@ -988,20 +894,14 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1010,20 +910,14 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.285734</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.902845</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-0.536592</v>
       </c>
     </row>
     <row r="30">
@@ -1042,10 +936,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D30" s="3" t="n">
+        <v>-17529.95753021888</v>
       </c>
     </row>
     <row r="31">
@@ -1054,20 +946,14 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1086,10 +972,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D32" s="3" t="n">
+        <v>-17529.95753021888</v>
       </c>
     </row>
     <row r="33">
@@ -1105,20 +989,14 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1127,20 +1005,14 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1149,20 +1021,14 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1171,20 +1037,14 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1193,20 +1053,14 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1215,20 +1069,14 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1237,20 +1085,14 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1275,20 +1117,14 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1297,20 +1133,14 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1319,20 +1149,14 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1341,20 +1165,14 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1363,20 +1181,14 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1385,20 +1197,14 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1407,20 +1213,14 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.9895929999999999</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0.486757</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.031435</v>
       </c>
     </row>
     <row r="49">
@@ -1445,20 +1245,14 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1467,20 +1261,14 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1489,20 +1277,14 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1511,20 +1293,14 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1533,20 +1309,14 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1577,20 +1347,14 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1599,20 +1363,14 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1621,20 +1379,14 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>2.108848</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>5.18139</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>5.403182</v>
       </c>
     </row>
     <row r="59">
@@ -1643,20 +1395,14 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1665,20 +1411,14 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1687,20 +1427,14 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1709,20 +1443,14 @@
           <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>2.108848</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>5.18139</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>5.403182</v>
       </c>
     </row>
     <row r="63">
@@ -1747,20 +1475,14 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1769,20 +1491,14 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1791,20 +1507,14 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1813,20 +1523,14 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1851,20 +1555,14 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1873,20 +1571,14 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1895,20 +1587,14 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1917,20 +1603,14 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1939,20 +1619,14 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1961,20 +1635,14 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1983,20 +1651,14 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0.686874</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2021,20 +1683,14 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2043,20 +1699,14 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2065,20 +1715,14 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2109,20 +1753,14 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2131,20 +1769,14 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2153,20 +1785,14 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2175,20 +1801,14 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2197,20 +1817,14 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2219,20 +1833,14 @@
           <t xml:space="preserve">  Total Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2241,20 +1849,14 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B87" s="3" t="n">
+        <v>0.767536</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0.072218</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0.158309</v>
       </c>
     </row>
     <row r="88">
@@ -2263,20 +1865,14 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>6.531342</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>6.644727</v>
       </c>
     </row>
     <row r="89">
@@ -2285,20 +1881,14 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2325,20 +1915,14 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2347,20 +1931,14 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -2369,20 +1947,14 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2407,20 +1979,14 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2429,20 +1995,14 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>2.343134</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>5.619299</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>5.304815</v>
       </c>
     </row>
     <row r="97">
@@ -2474,20 +2034,14 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.285734</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-0.902845</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.536592</v>
       </c>
     </row>
     <row r="100">
@@ -2496,20 +2050,14 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2518,20 +2066,14 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>-0.01022</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>-0.011141</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>-0.005137</v>
       </c>
     </row>
     <row r="102">
@@ -2540,20 +2082,14 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2562,20 +2098,14 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>-0.004452</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>-0.002974</v>
       </c>
     </row>
     <row r="104">
@@ -2600,20 +2130,14 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2622,20 +2146,14 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.050955</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0.043911</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0.11098</v>
       </c>
     </row>
     <row r="107">
@@ -2644,10 +2162,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0.371941</v>
@@ -2662,20 +2178,14 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2684,20 +2194,14 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2706,20 +2210,14 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2728,20 +2226,14 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2750,20 +2242,14 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2772,20 +2258,14 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2794,20 +2274,14 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2816,20 +2290,14 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2838,20 +2306,14 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2860,20 +2322,14 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2882,20 +2338,14 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>-0.008848</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>-0.024542</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>-0.221792</v>
       </c>
     </row>
     <row r="119">
@@ -2920,20 +2370,14 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2942,20 +2386,14 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2964,20 +2402,14 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2986,20 +2418,14 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3008,20 +2434,14 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3030,20 +2450,14 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3052,20 +2466,14 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3096,20 +2504,14 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3121,15 +2523,11 @@
       <c r="B129" s="3" t="n">
         <v>0.002996</v>
       </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -3138,20 +2536,14 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>1.230224</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0.021607</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0.02439</v>
       </c>
     </row>
     <row r="131">
@@ -3160,20 +2552,14 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3182,20 +2568,14 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-1.208617</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>0.002783</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>-0.002468</v>
       </c>
     </row>
     <row r="133">
@@ -3204,20 +2584,14 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.021607</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>0.02439</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>0.021922</v>
       </c>
     </row>
     <row r="134">
@@ -3226,20 +2600,14 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3248,20 +2616,14 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.238688</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-0.487661</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-0.237676</v>
       </c>
     </row>
   </sheetData>
@@ -3490,7 +2852,11 @@
           <t>Exploration and evaluation assets (Note 7)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="n">
         <v>2.108848</v>
       </c>
@@ -3700,7 +3066,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>TOTAL LIABILITIES AND</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -3893,7 +3259,11 @@
           <t>Net loss $</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>-0.285734</v>
       </c>
@@ -4011,7 +3381,11 @@
           <t>Receivables</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>-0.01022</v>
       </c>
@@ -4038,7 +3412,11 @@
           <t>Deposits and prepaid expenses</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -4158,7 +3536,11 @@
           <t>Exploration and evaluation assets</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>-0.008848</v>
       </c>
@@ -4216,7 +3598,11 @@
           <t>Change in cash during the year</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>-1.208617</v>
       </c>
@@ -4243,7 +3629,11 @@
           <t>Cash at the beginning of the year</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>1.230224</v>
       </c>
@@ -4270,7 +3660,11 @@
           <t>Cash at the end of the year $</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>0.021607</v>
       </c>
@@ -4684,7 +4078,11 @@
           <t>Consulting fees</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
         <v>0.045</v>
       </c>
@@ -4742,7 +4140,11 @@
           <t>Legal fees</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
         <v>0.06617199999999999</v>
       </c>
@@ -4769,7 +4171,11 @@
           <t>Management fees (Note 8)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
         <v>0.028809</v>
       </c>
@@ -4827,7 +4233,11 @@
           <t>Regulatory fees</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
         <v>0.022735</v>
       </c>
@@ -4941,7 +4351,11 @@
           <t>Loss before other income $</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
         <v>-0.319908</v>
       </c>
@@ -4968,7 +4382,11 @@
           <t>Foreign exchange loss</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
         <v>0.005579</v>
       </c>
@@ -5057,7 +4475,11 @@
           <t>Net loss and comprehensive loss $</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E60" s="5" t="n">
         <v>-0.285734</v>
       </c>
@@ -5326,7 +4748,11 @@
           <t>Net loss and comprehensive loss - - - -</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BGX.xlsx
+++ b/output/pdf_financials_xlsx/BGX.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/BGX.xlsx
+++ b/output/pdf_financials_xlsx/BGX.xlsx
@@ -631,13 +631,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -1909,10 +1909,8 @@
       <c r="C90" s="3" t="n">
         <v>-1.230652</v>
       </c>
-      <c r="D90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D90" s="3" t="n">
+        <v>-1.767244</v>
       </c>
     </row>
     <row r="91">
@@ -2643,7 +2641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3034,29 +3032,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deficit (1,767,244) ( 1 ,230,652)</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Total Shareholders’ Equity</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>StockholdersEquity</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.327807</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>5.619299</v>
+        <v>-1.230652</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>5.304815</v>
+        <v>-1.767244</v>
       </c>
     </row>
     <row r="14">
@@ -3067,25 +3063,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TOTAL LIABILITIES AND</t>
+          <t>SHAREHOLDERS’ EQUITY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TOTAL LIABILITIES AND</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total Shareholders’ Equity</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>2.343134</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>5.691517</v>
+        <v>5.619299</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>5.463124</v>
+        <v>5.304815</v>
       </c>
     </row>
     <row r="15">
@@ -3096,27 +3094,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>TOTAL LIABILITIES AND</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Subscriptions received in advance (Note 9)</t>
+          <t>TOTAL LIABILITIES AND</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" s="5" t="n">
-        <v>0.686874</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>5.691517</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>5.463124</v>
       </c>
     </row>
     <row r="16">
@@ -3127,17 +3123,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS’ EQUITY</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Special warrants (Note 9)</t>
+          <t>Subscriptions received in advance (Note 9)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" s="5" t="n">
-        <v>0.135941</v>
+        <v>0.686874</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3163,19 +3159,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Deficit</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>RetainedEarnings</t>
-        </is>
-      </c>
+          <t>Special warrants (Note 9)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" s="5" t="n">
-        <v>-0.327807</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>-1.230652</v>
+        <v>0.135941</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -3196,19 +3190,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Total Shareholders’ Equity</t>
+          <t>TOTAL LIABILITIES AND SHAREHOLDERS’ EQUITY $</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>StockholdersEquity</t>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2.343134</v>
+        <v>3.11067</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>5.619299</v>
+        <v>5.691517</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -3219,34 +3213,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS’ EQUITY</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TOTAL LIABILITIES AND SHAREHOLDERS’ EQUITY $</t>
+          <t>Net loss $</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>3.11067</v>
+        <v>-0.285734</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>5.691517</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.902845</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>-0.536592</v>
       </c>
     </row>
     <row r="20">
@@ -3257,27 +3249,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Net loss $</t>
+          <t>Share-based compensation</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>-0.285734</v>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.902845</v>
+        <v>0.371941</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.536592</v>
+        <v>0.189108</v>
       </c>
     </row>
     <row r="21">
@@ -3293,24 +3287,18 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" s="5" t="n">
+        <v>-0.003909</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.371941</v>
+        <v>-0.004915</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.189108</v>
+        <v>-0.001172</v>
       </c>
     </row>
     <row r="22">
@@ -3326,18 +3314,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Loss on debt settlement</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" s="5" t="n">
-        <v>-0.003909</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-0.004915</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>-0.001172</v>
+        <v>0.004247</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -3348,27 +3340,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Loss on debt settlement</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.01022</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.004247</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.011141</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.005137</v>
       </c>
     </row>
     <row r="24">
@@ -3384,22 +3376,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Receivables</t>
+          <t>Deposits and prepaid expenses</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>-0.01022</v>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-0.011141</v>
+        <v>-0.004452</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.005137</v>
+        <v>-0.002974</v>
       </c>
     </row>
     <row r="25">
@@ -3415,24 +3409,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Deposits and prepaid expenses</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0.061175</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>-0.004452</v>
+        <v>0.059504</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.002974</v>
+        <v>0.119091</v>
       </c>
     </row>
     <row r="26">
@@ -3448,22 +3440,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Net cash used in operating activities $</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0.061175</v>
+        <v>-0.238688</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.059504</v>
+        <v>-0.487661</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.119091</v>
+        <v>-0.237676</v>
       </c>
     </row>
     <row r="27">
@@ -3474,27 +3466,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities $</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>-0.238688</v>
+          <t>Investment GIC</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>-0.487661</v>
+        <v>0.5149860000000001</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.237676</v>
+        <v>0.457</v>
       </c>
     </row>
     <row r="28">
@@ -3510,20 +3500,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Investment GIC</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.008848</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.5149860000000001</v>
+        <v>-0.024542</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.457</v>
+        <v>-0.221792</v>
       </c>
     </row>
     <row r="29">
@@ -3539,22 +3531,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets</t>
+          <t>Net cash from (used in) investing activities $</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>-0.008848</v>
+        <v>-0.972925</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-0.024542</v>
+        <v>0.490444</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.221792</v>
+        <v>0.235208</v>
       </c>
     </row>
     <row r="30">
@@ -3570,22 +3562,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Net cash from (used in) investing activities $</t>
+          <t>Change in cash during the year</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>-0.972925</v>
+        <v>-1.208617</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.490444</v>
+        <v>0.002783</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.235208</v>
+        <v>-0.002468</v>
       </c>
     </row>
     <row r="31">
@@ -3601,22 +3593,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Change in cash during the year</t>
+          <t>Cash at the beginning of the year</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>-1.208617</v>
+        <v>1.230224</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.002783</v>
+        <v>0.021607</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.002468</v>
+        <v>0.02439</v>
       </c>
     </row>
     <row r="32">
@@ -3632,22 +3624,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cash at the beginning of the year</t>
+          <t>Cash at the end of the year $</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>1.230224</v>
+        <v>0.021607</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.021607</v>
+        <v>0.02439</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.02439</v>
+        <v>0.021922</v>
       </c>
     </row>
     <row r="33">
@@ -3658,27 +3650,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Cash (paid) received for</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cash at the end of the year $</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Interest $</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" s="5" t="n">
-        <v>0.021607</v>
+        <v>0.024686</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.02439</v>
+        <v>0.025895</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.021922</v>
+        <v>0.007079</v>
       </c>
     </row>
     <row r="34">
@@ -3689,23 +3677,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cash (paid) received for</t>
+          <t>Non-cash transactions affecting investing and financing activities</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Interest $</t>
+          <t>Shares issued for exploration and evaluation asset (Note 7) $</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" s="5" t="n">
-        <v>0.024686</v>
+        <v>2.1</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.025895</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>0.007079</v>
+        <v>3.048</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -3716,25 +3706,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Non-cash transactions affecting investing and financing activities</t>
+          <t>Company’s ability to continue as a going concern.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation asset (Note 7) $</t>
+          <t>Standards Board (“IASB”) and interpretations issued by the International Financial Reporting by the Board of Directors on April</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" s="5" t="n">
-        <v>2.1</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>3.048</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002026</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>1.5e-05</v>
       </c>
     </row>
     <row r="36">
@@ -3745,25 +3735,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Company’s ability to continue as a going concern.</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Standards Board (“IASB”) and interpretations issued by the International Financial Reporting by the Board of Directors on April</t>
+          <t>Subscription received in advance</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>0.002026</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>1.5e-05</v>
+      <c r="E36" s="5" t="n">
+        <v>0.002996</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -3779,10 +3771,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Subscription received in advance</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Net cash from financing activities</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
         <v>0.002996</v>
       </c>
@@ -3805,26 +3801,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Net cash from financing activities</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Net investments in GIC</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" s="5" t="n">
-        <v>0.002996</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.964077</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0.5149860000000001</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3840,20 +3830,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Cash (paid) received for</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Net investments in GIC</t>
+          <t>Taxes $</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" s="5" t="n">
-        <v>-0.964077</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>0.5149860000000001</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3869,24 +3863,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cash (paid) received for</t>
+          <t>continue as a going concern.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Taxes $</t>
+          <t>Standards Board (“IASB”) and  interpretations issued by the International Financial Reporting by the Board of Directors on April</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E40" s="5" t="n">
+        <v>0.002025</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>2.4e-05</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3897,30 +3887,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>continue as a going concern.</t>
-        </is>
-      </c>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Standards Board (“IASB”) and interpretations issued by the International Financial Reporting by the Board of Directors on April</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" s="5" t="n">
-        <v>0.002025</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>2.4e-05</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.003061</v>
       </c>
     </row>
     <row r="42">
@@ -3932,14 +3924,10 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Production Taxes</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -3951,7 +3939,7 @@
         </is>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.003061</v>
+        <v>-3.1e-05</v>
       </c>
     </row>
     <row r="43">
@@ -3963,10 +3951,14 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Production Taxes</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Gross Profit $</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -3978,7 +3970,7 @@
         </is>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-3.1e-05</v>
+        <v>0.00303</v>
       </c>
     </row>
     <row r="44">
@@ -3987,29 +3979,27 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gross Profit $</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
+          <t>Advertisement and promotions</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F44" s="5" t="n">
+        <v>0.065886</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.00303</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="45">
@@ -4025,20 +4015,18 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Advertisement and promotions</t>
+          <t>Audit fees</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E45" s="5" t="n">
+        <v>0.03075</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.065886</v>
+        <v>0.02525</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.015</v>
+        <v>0.03025</v>
       </c>
     </row>
     <row r="46">
@@ -4054,18 +4042,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Audit fees</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="n">
-        <v>0.03075</v>
+        <v>0.045</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.02525</v>
+        <v>0.086131</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.03025</v>
+        <v>0.037351</v>
       </c>
     </row>
     <row r="47">
@@ -4081,22 +4073,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
+          <t>General administration</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0.045</v>
+        <v>0.001879</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.086131</v>
+        <v>0.010967</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.037351</v>
+        <v>0.015666</v>
       </c>
     </row>
     <row r="48">
@@ -4112,22 +4104,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>General administration</t>
+          <t>Legal fees</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.001879</v>
+        <v>0.06617199999999999</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.010967</v>
+        <v>0.075528</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.015666</v>
+        <v>0.028391</v>
       </c>
     </row>
     <row r="49">
@@ -4143,7 +4135,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Legal fees</t>
+          <t>Management fees (Note 8)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4152,13 +4144,13 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.06617199999999999</v>
+        <v>0.028809</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.075528</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.028391</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -4174,22 +4166,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Management fees (Note 8)</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.028809</v>
+        <v>0.116571</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.19431</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.062621</v>
       </c>
     </row>
     <row r="51">
@@ -4205,22 +4197,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Regulatory fees</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0.116571</v>
+        <v>0.022735</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.19431</v>
+        <v>0.03336</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.062621</v>
+        <v>0.074862</v>
       </c>
     </row>
     <row r="52">
@@ -4236,22 +4228,20 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Regulatory fees</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>0.022735</v>
+          <t>Share based compensation (Note 8, 9)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.03336</v>
+        <v>0.371941</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.074862</v>
+        <v>0.189108</v>
       </c>
     </row>
     <row r="53">
@@ -4267,20 +4257,18 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Share based compensation (Note 8, 9)</t>
+          <t>Travel expense</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E53" s="5" t="n">
+        <v>0.007992000000000001</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.371941</v>
+        <v>0.00013</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.189108</v>
+        <v>0.000807</v>
       </c>
     </row>
     <row r="54">
@@ -4296,18 +4284,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Travel expense</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Total operating expenses $</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="n">
-        <v>0.007992000000000001</v>
+        <v>0.319908</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.00013</v>
+        <v>0.932503</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.000807</v>
+        <v>0.5413559999999999</v>
       </c>
     </row>
     <row r="55">
@@ -4323,22 +4315,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Total operating expenses $</t>
+          <t>Loss before other income $</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0.319908</v>
+        <v>-0.319908</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.932503</v>
+        <v>-0.932503</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.5413559999999999</v>
+        <v>-0.538326</v>
       </c>
     </row>
     <row r="56">
@@ -4349,12 +4341,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Loss before other income $</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4363,13 +4355,13 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>-0.319908</v>
+        <v>0.005579</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>-0.932503</v>
+        <v>0.007004</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.538326</v>
+        <v>-0.000436</v>
       </c>
     </row>
     <row r="57">
@@ -4385,22 +4377,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>InterestIncome</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0.005579</v>
+        <v>0.028595</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.007004</v>
+        <v>0.026901</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.000436</v>
+        <v>0.00217</v>
       </c>
     </row>
     <row r="58">
@@ -4416,22 +4408,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>InterestIncome</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>0.028595</v>
+          <t>Loss on debt settlement (Note 8)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.026901</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.00217</v>
+        <v>-0.004247</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -4447,22 +4439,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Loss on debt settlement (Note 8)</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>-0.285734</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>-0.004247</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.902845</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>-0.536592</v>
       </c>
     </row>
     <row r="60">
@@ -4478,22 +4470,18 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Loss per share – basic and diluted1 $</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" s="5" t="n">
-        <v>-0.285734</v>
+        <v>0</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-0.902845</v>
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.536592</v>
+        <v>-3e-08</v>
       </c>
     </row>
     <row r="61">
@@ -4504,23 +4492,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Weighted average number of shares outstanding –</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted1 $</t>
+          <t>Weighted average number of shares outstanding – basic and diluted(1)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" s="5" t="n">
-        <v>0</v>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>15.991698</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-3e-08</v>
+        <v>17.162094</v>
       </c>
     </row>
     <row r="62">
@@ -4531,12 +4521,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding –</t>
+          <t>Number    Amount      rants   Reserve        Deficit      Total</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding – basic and diluted(1)</t>
+          <t>Balance at December 31, 2023 (Note 1) 13,950,000 2,535,000 135,941 -</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -4546,10 +4536,10 @@
         </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>15.991698</v>
+        <v>2.343134</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>17.162094</v>
+        <v>-0.327807</v>
       </c>
     </row>
     <row r="63">
@@ -4560,12 +4550,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Number Amount rants Reserve Deficit Total</t>
+          <t>Number    Amount      rants   Reserve        Deficit      Total</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2023 (Note 1) 13,950,000 2,535,000 135,941 -</t>
+          <t>Shares issued for debt settlement (Note 9) 50,961 72,195 - -</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -4575,10 +4565,12 @@
         </is>
       </c>
       <c r="F63" s="5" t="n">
-        <v>2.343134</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>-0.327807</v>
+        <v>0.072195</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -4589,12 +4581,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Number Amount rants Reserve Deficit Total</t>
+          <t>Number    Amount      rants   Reserve        Deficit      Total</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Shares issued for debt settlement (Note 9) 50,961 72,195 - -</t>
+          <t>Conversion of special warrants (Note 9) 271,881 135,941 (135,941) -</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -4603,8 +4595,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F64" s="5" t="n">
-        <v>0.072195</v>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4620,12 +4614,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Number Amount rants Reserve Deficit Total</t>
+          <t>Number    Amount      rants   Reserve        Deficit      Total</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Conversion of special warrants (Note 9) 271,881 135,941 (135,941) -</t>
+          <t>Private Placement (Note 9) 1,373,748 686,874 - -</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -4634,10 +4628,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F65" s="5" t="n">
+        <v>0.686874</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4653,12 +4645,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Number Amount rants Reserve Deficit Total</t>
+          <t>Number    Amount      rants   Reserve        Deficit      Total</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Private Placement (Note 9) 1,373,748 686,874 - -</t>
+          <t>Share based compensation (Note 9) 39,999 53,332 - 318,609</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -4668,7 +4660,7 @@
         </is>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0.686874</v>
+        <v>0.371941</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4684,12 +4676,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Number Amount rants Reserve Deficit Total</t>
+          <t>Number    Amount      rants   Reserve        Deficit      Total</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Share based compensation (Note 9) 39,999 53,332 - 318,609</t>
+          <t>Share issued for exploration and evaluation asset (Note 7) 1,440,000 3,048,000 - -</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -4699,7 +4691,7 @@
         </is>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.371941</v>
+        <v>3.048</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -4715,27 +4707,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Number Amount rants Reserve Deficit Total</t>
+          <t>Number    Amount      rants   Reserve        Deficit      Total</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Share issued for exploration and evaluation asset (Note 7) 1,440,000 3,048,000 - -</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Net loss and comprehensive loss - - - -</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>3.048</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.902845</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>-0.902845</v>
       </c>
     </row>
     <row r="69">
@@ -4746,29 +4740,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Number Amount rants Reserve Deficit Total</t>
+          <t>Number    Amount      rants   Reserve        Deficit      Total</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - - -</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance at December 31, 2024 17,126,589 6,531,342 - 318,609</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>-0.902845</v>
+        <v>5.619299</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>-0.902845</v>
+        <v>-1.230652</v>
       </c>
     </row>
     <row r="70">
@@ -4779,12 +4769,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Number Amount rants Reserve Deficit Total</t>
+          <t>Number    Amount      rants   Reserve        Deficit      Total</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2024 17,126,589 6,531,342 - 318,609</t>
+          <t>Share issued for exercise of stock options (Note 9) 24,750 62,510 - (29,510)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -4794,10 +4784,12 @@
         </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>5.619299</v>
-      </c>
-      <c r="G70" s="5" t="n">
-        <v>-1.230652</v>
+        <v>0.033</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -4808,12 +4800,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Number Amount rants Reserve Deficit Total</t>
+          <t>Number    Amount      rants   Reserve        Deficit      Total</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Share issued for exercise of stock options (Note 9) 24,750 62,510 - (29,510)</t>
+          <t>Shares issued for vested restricted share units (Note 9) 22,500 50,875 - (50,875)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -4822,8 +4814,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F71" s="5" t="n">
-        <v>0.033</v>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -4839,12 +4833,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Number Amount rants Reserve Deficit Total</t>
+          <t>Number    Amount      rants   Reserve        Deficit      Total</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Shares issued for vested restricted share units (Note 9) 22,500 50,875 - (50,875)</t>
+          <t>Share based compensation (Note 9) - - - 189,108</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -4853,10 +4847,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F72" s="5" t="n">
+        <v>0.189108</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4872,12 +4864,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Number Amount rants Reserve Deficit Total</t>
+          <t>Number    Amount      rants   Reserve        Deficit      Total</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Share based compensation (Note 9) - - - 189,108</t>
+          <t>Balance at December 31, 2025 17,173,839 6,644,727 - 427,332</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -4887,12 +4879,10 @@
         </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.189108</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.304815</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>-1.767244</v>
       </c>
     </row>
     <row r="74">
@@ -4903,25 +4893,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Number Amount rants Reserve Deficit Total</t>
+          <t>Weighted average number of shares outstanding –</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2025 17,173,839 6,644,727 - 427,332</t>
+          <t>Weighted average number of shares outstanding – basic and diluted1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E74" s="5" t="n">
+        <v>107.05068</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>5.304815</v>
-      </c>
-      <c r="G74" s="5" t="n">
-        <v>-1.767244</v>
+        <v>159.916981</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -4932,20 +4922,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding –</t>
+          <t>Number    Amount   Warrants     Reserve         Deficit       Total</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding – basic and diluted1</t>
+          <t>Balance at December 31, 2022 2,550,000 435,000 -</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" s="5" t="n">
-        <v>107.05068</v>
+        <v>0.392927</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>159.916981</v>
+        <v>-0.042073</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4961,20 +4951,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Number Amount Warrants Reserve Deficit Total</t>
+          <t>Number    Amount   Warrants     Reserve         Deficit       Total</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2022 2,550,000 435,000 -</t>
+          <t>Shares issued for exploration and evaluation asset (Note 7, 9) 2,100,000 2,100,000 - -</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" s="5" t="n">
-        <v>0.392927</v>
-      </c>
-      <c r="F76" s="5" t="n">
-        <v>-0.042073</v>
+        <v>2.1</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -4990,17 +4982,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Number Amount Warrants Reserve Deficit Total</t>
+          <t>Number    Amount   Warrants     Reserve         Deficit       Total</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation asset (Note 7, 9) 2,100,000 2,100,000 - -</t>
+          <t>Special warrants issued (Note 9) - - 135,941 -</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" s="5" t="n">
-        <v>2.1</v>
+        <v>0.135941</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -5021,22 +5013,24 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Number Amount Warrants Reserve Deficit Total</t>
+          <t>Number    Amount   Warrants     Reserve         Deficit       Total</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Special warrants issued (Note 9) - - 135,941 -</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>Net loss - - - -</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E78" s="5" t="n">
-        <v>0.135941</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.285734</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>-0.285734</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -5052,24 +5046,20 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Number Amount Warrants Reserve Deficit Total</t>
+          <t>Number    Amount   Warrants     Reserve         Deficit       Total</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Net loss - - - -</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance at December 31, 2023 4,650,000 2,535,000 135,941 -</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" s="5" t="n">
-        <v>-0.285734</v>
+        <v>2.343134</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>-0.285734</v>
+        <v>-0.327807</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -5085,20 +5075,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Number Amount Warrants Reserve Deficit Total</t>
+          <t>Number    Amount   Warrants     Reserve         Deficit       Total</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Balance at December 31, 2023 4,650,000 2,535,000 135,941 -</t>
+          <t>Shares issued for debt settlement (Note 9) 16,987 72,195 - -</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" s="5" t="n">
-        <v>2.343134</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>-0.327807</v>
+        <v>0.072195</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -5114,17 +5106,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Number Amount Warrants Reserve Deficit Total</t>
+          <t>Number    Amount   Warrants     Reserve         Deficit       Total</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Shares issued for debt settlement (Note 9) 16,987 72,195 - -</t>
+          <t>Conversion of special warrants (Note 9) 90,627 135,941 (135,941) -</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" s="5" t="n">
-        <v>0.072195</v>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -5145,19 +5139,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Number Amount Warrants Reserve Deficit Total</t>
+          <t>Number    Amount   Warrants     Reserve         Deficit       Total</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Conversion of special warrants (Note 9) 90,627 135,941 (135,941) -</t>
+          <t>Private placement (Note 9) 457,916 686,874 - -</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E82" s="5" t="n">
+        <v>0.686874</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -5178,17 +5170,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Number Amount Warrants Reserve Deficit Total</t>
+          <t>Number    Amount   Warrants     Reserve         Deficit       Total</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Private placement (Note 9) 457,916 686,874 - -</t>
+          <t>Shares issued for exploration and evaluation asset (Note 7, 9) 480,000 3,048,000 - -</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" s="5" t="n">
-        <v>0.686874</v>
+        <v>3.048</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -5209,17 +5201,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Number Amount Warrants Reserve Deficit Total</t>
+          <t>Number    Amount   Warrants     Reserve         Deficit       Total</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation asset (Note 7, 9) 480,000 3,048,000 - -</t>
+          <t>Share based compensation (Note 9) 13,333 53,332 - 318,609</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" s="5" t="n">
-        <v>3.048</v>
+        <v>0.371941</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -5240,53 +5232,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Number Amount Warrants Reserve Deficit Total</t>
+          <t>Number    Amount   Warrants     Reserve         Deficit       Total</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Share based compensation (Note 9) 13,333 53,332 - 318,609</t>
+          <t>Balance at December 31, 2024 5,708,863 6,531,342 - 318,609</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" s="5" t="n">
-        <v>0.371941</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.619298</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>-1.230652</v>
       </c>
       <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Number Amount Warrants Reserve Deficit Total</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Balance at December 31, 2024 5,708,863 6,531,342 - 318,609</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" s="5" t="n">
-        <v>5.619298</v>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>-1.230652</v>
-      </c>
-      <c r="G86" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/BGX.xlsx
+++ b/output/pdf_financials_xlsx/BGX.xlsx
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.028595</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.026901</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00217</v>
       </c>
     </row>
     <row r="13">
@@ -885,13 +885,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.285734</v>
+        <v>-0.314329</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.902845</v>
+        <v>-0.929746</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.536592</v>
+        <v>-0.538762</v>
       </c>
     </row>
     <row r="28">
@@ -917,13 +917,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.285734</v>
+        <v>-0.314329</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.902845</v>
+        <v>-0.929746</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.536592</v>
+        <v>-0.538762</v>
       </c>
     </row>
     <row r="30">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-17529.95753021888</v>
+        <v>-17600.84939562235</v>
       </c>
     </row>
     <row r="31">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.021607</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.02439</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.021922</v>
       </c>
     </row>
     <row r="35">
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.021607</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.02439</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.021922</v>
       </c>
     </row>
     <row r="37">
@@ -1220,13 +1220,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.9895929999999999</v>
+        <v>0.967986</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.486757</v>
+        <v>0.462367</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.031435</v>
+        <v>0.009513000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
